--- a/public/Uniform_Bulk_Upload_Template.xlsx
+++ b/public/Uniform_Bulk_Upload_Template.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ayesh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F9EA18E-F74E-4A6F-8BB7-53E78EB63D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F20C9174-3FDD-4309-A7C0-2E7981AEB819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uniforms" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="30">
   <si>
     <t>Category</t>
   </si>
@@ -98,13 +111,25 @@
   </si>
   <si>
     <t>Accessories</t>
+  </si>
+  <si>
+    <t>Amount/unit</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Invoice No</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -113,6 +138,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="12"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -122,7 +148,23 @@
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -182,18 +224,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -533,640 +581,1001 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M38"/>
+  <dimension ref="A2:Q45"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.8984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.8984375" customWidth="1"/>
     <col min="3" max="3" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D1" s="4" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="1"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="K1" s="6" t="s">
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="M4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="G5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="L5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="M5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="N5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="O5" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="P5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C6" s="1">
         <v>14</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1">
-        <v>14.5</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1">
-        <v>15</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1">
-        <v>15.5</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1">
+        <f>(D6+E6+F6)*G6</f>
+        <v>0</v>
+      </c>
       <c r="J6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="M6" s="1"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1">
+        <f>(M6+N6+O6)*P6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1">
+        <f t="shared" ref="H7:H13" si="0">(D7+E7+F7)*G7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="1"/>
       <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
+      <c r="L7" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="M7" s="1"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1">
+        <f t="shared" ref="Q7:Q12" si="1">(M7+N7+O7)*P7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="1"/>
       <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
+      <c r="L8" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="M8" s="1"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="1"/>
       <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
+      <c r="L9" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="M9" s="1"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="G10" s="1"/>
+      <c r="H10" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D15" s="4" t="s">
+      <c r="G11" s="1"/>
+      <c r="H11" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1">
+        <v>17</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q13" s="1">
+        <f>SUM(Q6:Q12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1">
+        <v>18</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1">
+        <f>(D14+E14+F14)*G14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="G15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="1">
+        <f>SUM(H6:H14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D18" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E15" s="4"/>
-      <c r="K15" s="4" t="s">
+      <c r="E18" s="7"/>
+      <c r="M18" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="5" t="s">
+      <c r="N18" s="7"/>
+      <c r="O18" s="6"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C19" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D19" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E19" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="F19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="L19" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="K16" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L16" s="3" t="s">
+      <c r="M19" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M16" s="3" t="s">
+      <c r="N19" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="O19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C20" s="1">
         <v>28</v>
-      </c>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="H17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" s="1">
-        <v>28</v>
-      </c>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1">
-        <v>29</v>
-      </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1">
-        <v>29</v>
-      </c>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1">
-        <v>30</v>
-      </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1">
-        <v>30</v>
-      </c>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1">
-        <v>31</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1">
-        <v>31</v>
-      </c>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1">
+        <f>(D20+E20)*F20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L20" s="1">
+        <v>28</v>
+      </c>
       <c r="M20" s="1"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1">
+        <f>(M20+N20)*O20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1">
-        <v>32</v>
-      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1">
+        <f t="shared" ref="G21:G34" si="2">(D21+E21)*F21</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="1"/>
       <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
+      <c r="L21" s="1">
+        <v>29</v>
+      </c>
       <c r="M21" s="1"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1">
+        <f t="shared" ref="P21:P34" si="3">(M21+N21)*O21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1">
-        <v>33</v>
-      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
+      <c r="L22" s="1">
+        <v>30</v>
+      </c>
       <c r="M22" s="1"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1">
-        <v>34</v>
-      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
+      <c r="L23" s="1">
+        <v>31</v>
+      </c>
       <c r="M23" s="1"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1">
-        <v>35</v>
-      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="1"/>
       <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
+      <c r="L24" s="1">
+        <v>32</v>
+      </c>
       <c r="M24" s="1"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1">
-        <v>36</v>
-      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
+      <c r="L25" s="1">
+        <v>33</v>
+      </c>
       <c r="M25" s="1"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1">
-        <v>37</v>
-      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="1"/>
       <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
+      <c r="L26" s="1">
+        <v>34</v>
+      </c>
       <c r="M26" s="1"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1">
-        <v>38</v>
-      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="1"/>
       <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
+      <c r="L27" s="1">
+        <v>35</v>
+      </c>
       <c r="M27" s="1"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1">
-        <v>39</v>
-      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="1"/>
       <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
+      <c r="L28" s="1">
+        <v>36</v>
+      </c>
       <c r="M28" s="1"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1">
-        <v>40</v>
-      </c>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="1"/>
       <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
+      <c r="L29" s="1">
+        <v>37</v>
+      </c>
       <c r="M29" s="1"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1">
-        <v>41</v>
-      </c>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="1"/>
       <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
+      <c r="L30" s="1">
+        <v>38</v>
+      </c>
       <c r="M30" s="1"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1">
+      <c r="F31" s="1"/>
+      <c r="G31" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1">
+        <v>39</v>
+      </c>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1">
+        <v>40</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1">
+        <v>40</v>
+      </c>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1">
+        <v>41</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1">
+        <v>41</v>
+      </c>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1">
         <v>42</v>
       </c>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C33" s="6" t="s">
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1">
+        <v>42</v>
+      </c>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="F35" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G35" s="1">
+        <f>SUM(G20:G34)</f>
+        <v>0</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P35" s="1">
+        <f>SUM(P20:P34)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A37" s="5"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="6"/>
-      <c r="I33" s="6" t="s">
+      <c r="D37" s="8"/>
+      <c r="L37" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J33" s="6"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" s="2" t="s">
+      <c r="M37" s="4"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F34" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="G34" s="3" t="s">
+      <c r="E38" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H34" s="3" t="s">
+      <c r="K38" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I34" s="3" t="s">
+      <c r="L38" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J34" s="3" t="s">
+      <c r="M38" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+      <c r="N38" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="F35" s="1" t="s">
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1">
+        <f>(C39+D39)*E39</f>
+        <v>0</v>
+      </c>
+      <c r="H39" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="I39" s="1"/>
+      <c r="J39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H35" s="1">
+      <c r="K39" s="1">
         <v>7</v>
       </c>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1" t="s">
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1">
+        <f>(L39+M39)*N39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1">
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1">
+        <f t="shared" ref="F40:F42" si="4">(C40+D40)*E40</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1">
         <v>8</v>
       </c>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1" t="s">
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1">
+        <f t="shared" ref="O40:O42" si="5">(L40+M40)*N40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1">
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1">
         <v>9</v>
       </c>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1" t="s">
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1">
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1">
         <v>10</v>
       </c>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E43" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43" s="1">
+        <f>SUM(F39:F42)</f>
+        <v>0</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O43" s="1">
+        <f>SUM(O39:O42)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="21" x14ac:dyDescent="0.4">
+      <c r="A45" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B45" s="10">
+        <f>H15+Q13+G35+P35+F43+O43</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="I33:J33"/>
+  <mergeCells count="5">
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="M18:N18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
